--- a/scripts/demo/planilha_demo.xlsx
+++ b/scripts/demo/planilha_demo.xlsx
@@ -647,9 +647,178 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SEI</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>MATRÍCULA</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>NOME</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>PREVIDÊNCIA</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ÓRGÃO DE ORIGEM</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>REGIME DE PREVIDÊNCIA</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>SITUAÇÃO DO SERVIDOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>111.111.111-11</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>700201-3</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Fulano de Tal</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>FUNAFIN</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Analista Administrativo</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Coordenadoria de Sede Modelo</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>RPPS</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Em exercício</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>222.222.222-22</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>700202-1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ciclana Souza</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>INSS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Técnico Administrativo</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Coordenadoria de Sede Modelo</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>RPPS</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Em exercício</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>333.333.333-33</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>700203-8</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Beltrano Pereira</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>FUNAFIN</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Assessor Técnico</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Coordenadoria de Sede Modelo</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>RPPS</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Em exercício</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/scripts/demo/planilha_demo.xlsx
+++ b/scripts/demo/planilha_demo.xlsx
@@ -502,6 +502,31 @@
           <t>MOTIVO</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>VALOR DA PASSAGEM</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>QUANT. DIÁRIA INTEGRAL</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>QUANT. DIÁRIA PARCIAL</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>VALOR TOTAL DAS DIÁRIAS</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>LOCAL</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
